--- a/output/pdf_financials_xlsx/SES.xlsx
+++ b/output/pdf_financials_xlsx/SES.xlsx
@@ -4446,40 +4446,40 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>4.424</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>14.629</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>36.403</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>32.049</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>21.618</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>33.982</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>26.734</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>2.4e-05</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>3e-05</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>2.9e-05</v>
       </c>
     </row>
     <row r="92">
@@ -4489,10 +4489,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>14.659</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>25.227</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -8340,7 +8340,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>4.424</v>
       </c>
@@ -19972,7 +19976,11 @@
           <t>Share-based payment reserve 16</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E185" s="5" t="n">
         <v>14.659</v>
       </c>

--- a/output/pdf_financials_xlsx/SES.xlsx
+++ b/output/pdf_financials_xlsx/SES.xlsx
@@ -1953,40 +1953,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>12.019</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.882</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.863</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.432</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>9.73</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.928</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>8.853999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.2e-05</v>
       </c>
     </row>
     <row r="35">
@@ -2039,40 +2039,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>12.019</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.882</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.863</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.432</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>9.73</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.928</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>8.853999999999999</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.2e-05</v>
       </c>
     </row>
     <row r="37">
@@ -2558,37 +2558,37 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>241.92</v>
+        <v>237.038</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>154.064</v>
+        <v>149.201</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>232.734</v>
+        <v>229.302</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>333.183</v>
+        <v>323.453</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>261.324</v>
+        <v>253.396</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>249.296</v>
+        <v>240.442</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.000366</v>
+        <v>0.000356</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.000476</v>
+        <v>0.000464</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.001046</v>
+        <v>0.001034</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.000545</v>
+        <v>0.000519</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.000487</v>
+        <v>0.000465</v>
       </c>
     </row>
     <row r="49">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -49968,7 +49968,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E585" s="5" t="n">

--- a/output/pdf_financials_xlsx/SES.xlsx
+++ b/output/pdf_financials_xlsx/SES.xlsx
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>120.143</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>192.991</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -3544,25 +3544,25 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>7.223</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>18.03</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>2.8e-05</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>2.7e-05</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>2.6e-05</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>3.2e-05</v>
       </c>
     </row>
     <row r="71">
@@ -3587,25 +3587,25 @@
         <v>0</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>7.223</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>18.03</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.000452</v>
+        <v>0.000479</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.000346</v>
+        <v>0.000374</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.000415</v>
+        <v>0.000442</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4.5e-05</v>
+        <v>7.1e-05</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0.000269</v>
+        <v>0.000301</v>
       </c>
     </row>
     <row r="72">
@@ -3759,10 +3759,10 @@
         <v>8.166</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>10.201</v>
+        <v>2.978</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>21.09</v>
+        <v>3.06</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -3774,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>8.3e-05</v>
+        <v>5.7e-05</v>
       </c>
       <c r="M75" s="3" t="n">
         <v>0</v>
@@ -3983,30 +3983,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G80" s="3" t="n">
+        <v>0.008554853869878103</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.02132218855768344</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.4086799276672695</v>
+        <v>0.4330922242314648</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.2733017377567141</v>
+        <v>0.2954186413902053</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.3499156829679596</v>
+        <v>0.372681281618887</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.04318618042226487</v>
+        <v>0.06813819577735125</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.3396464646464646</v>
+        <v>0.380050505050505</v>
       </c>
     </row>
     <row r="81">
@@ -5231,10 +5227,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.729</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>1.154</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -5736,10 +5732,10 @@
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-1.3e-05</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-5e-06</v>
       </c>
     </row>
     <row r="122">
@@ -7642,7 +7638,11 @@
           <t>Lease liabilities 17</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -9386,7 +9386,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -11462,7 +11466,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -20504,7 +20512,11 @@
           <t>Deferred tax expense 24</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -21920,7 +21932,11 @@
           <t>Tax on share repurchases 18</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -22968,7 +22984,11 @@
           <t>Deferred tax expense 20</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -23930,7 +23950,11 @@
           <t>Tax on share repurchases 15</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -24738,7 +24762,11 @@
           <t>Current and deferred tax expense</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -25950,7 +25978,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -26246,7 +26278,11 @@
           <t>Current and deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -28328,7 +28364,11 @@
           <t>Current and deferred tax expense 16</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -29654,7 +29694,11 @@
           <t>Current and deferred tax recovery</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -31450,7 +31494,11 @@
           <t>Accretion 14</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E340" s="5" t="n">
         <v>0.729</v>
       </c>
@@ -31672,7 +31720,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E343" s="5" t="n">
         <v>3.598</v>
       </c>
